--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU02/HRM/post FET_HRM-2031-0280/Panel 7/Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,12 +434,17 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -451,23 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.28503</v>
+        <v>16.75839</v>
       </c>
       <c r="D2" t="n">
-        <v>16.00069</v>
+        <v>16.40933</v>
       </c>
       <c r="E2" t="n">
-        <v>16.52141</v>
+        <v>16.62153</v>
       </c>
       <c r="F2" t="n">
-        <v>21.60918</v>
+        <v>42.44069</v>
       </c>
       <c r="G2" t="n">
-        <v>33.80693</v>
+        <v>0.04988</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.84375</v>
       </c>
     </row>
     <row r="3">
@@ -477,19 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.7408</v>
+        <v>16.98695</v>
       </c>
       <c r="D3" t="n">
-        <v>15.66055</v>
+        <v>16.5319</v>
       </c>
       <c r="E3" t="n">
-        <v>16.47875</v>
+        <v>16.67145</v>
       </c>
       <c r="F3" t="n">
-        <v>21.84976</v>
+        <v>42.1846</v>
       </c>
       <c r="G3" t="n">
-        <v>34.30624</v>
+        <v>0.05183</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.79501</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.69855</v>
+        <v>17.03235</v>
       </c>
       <c r="D4" t="n">
-        <v>16.18592</v>
+        <v>16.34604</v>
       </c>
       <c r="E4" t="n">
-        <v>16.29263</v>
+        <v>16.82142</v>
       </c>
       <c r="F4" t="n">
-        <v>21.8349</v>
+        <v>42.07382</v>
       </c>
       <c r="G4" t="n">
-        <v>34.39694</v>
+        <v>0.05052</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.81916</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.55191</v>
+        <v>17.14406</v>
       </c>
       <c r="D5" t="n">
-        <v>15.88016</v>
+        <v>16.5563</v>
       </c>
       <c r="E5" t="n">
-        <v>16.12721</v>
+        <v>16.70078</v>
       </c>
       <c r="F5" t="n">
-        <v>21.70921</v>
+        <v>42.36616</v>
       </c>
       <c r="G5" t="n">
-        <v>34.30145</v>
+        <v>0.05088</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.83996</v>
       </c>
     </row>
     <row r="6">
@@ -543,19 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.71238</v>
+        <v>17.06297</v>
       </c>
       <c r="D6" t="n">
-        <v>15.88962</v>
+        <v>16.69327</v>
       </c>
       <c r="E6" t="n">
-        <v>16.27528</v>
+        <v>16.71601</v>
       </c>
       <c r="F6" t="n">
-        <v>22.00211</v>
+        <v>42.48518</v>
       </c>
       <c r="G6" t="n">
-        <v>33.94095</v>
+        <v>0.04911</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.83336</v>
       </c>
     </row>
     <row r="7">
@@ -565,19 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.97814</v>
+        <v>16.75975</v>
       </c>
       <c r="D7" t="n">
-        <v>16.13814</v>
+        <v>16.3607</v>
       </c>
       <c r="E7" t="n">
-        <v>16.31769</v>
+        <v>16.58504</v>
       </c>
       <c r="F7" t="n">
-        <v>21.75164</v>
+        <v>42.89032</v>
       </c>
       <c r="G7" t="n">
-        <v>34.16043</v>
+        <v>0.04926</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.79564</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.87662</v>
+        <v>16.69417</v>
       </c>
       <c r="D8" t="n">
-        <v>15.99314</v>
+        <v>16.53343</v>
       </c>
       <c r="E8" t="n">
-        <v>16.52698</v>
+        <v>16.65354</v>
       </c>
       <c r="F8" t="n">
-        <v>21.80844</v>
+        <v>41.69021</v>
       </c>
       <c r="G8" t="n">
-        <v>33.45374</v>
+        <v>0.05121</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.89442</v>
       </c>
     </row>
     <row r="9">
@@ -609,19 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.84835</v>
+        <v>16.90139</v>
       </c>
       <c r="D9" t="n">
-        <v>16.0002</v>
+        <v>16.56025</v>
       </c>
       <c r="E9" t="n">
-        <v>16.14686</v>
+        <v>16.60223</v>
       </c>
       <c r="F9" t="n">
-        <v>21.51098</v>
+        <v>43.1033</v>
       </c>
       <c r="G9" t="n">
-        <v>34.11825</v>
+        <v>0.05057</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.82672</v>
       </c>
     </row>
     <row r="10">
@@ -631,607 +660,712 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.59079</v>
+        <v>16.93444</v>
       </c>
       <c r="D10" t="n">
-        <v>16.3119</v>
+        <v>16.49947</v>
       </c>
       <c r="E10" t="n">
-        <v>16.80776</v>
+        <v>16.5467</v>
       </c>
       <c r="F10" t="n">
-        <v>21.49358</v>
+        <v>43.10962</v>
       </c>
       <c r="G10" t="n">
-        <v>33.79758</v>
+        <v>0.05055</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.83502</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pad 2</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>16.7387</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.61948</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.69557</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42.60395</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05114</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.80332</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.54103</v>
+        <v>16.82056</v>
       </c>
       <c r="D12" t="n">
-        <v>16.29087</v>
+        <v>16.52441</v>
       </c>
       <c r="E12" t="n">
-        <v>16.76829</v>
+        <v>16.62571</v>
       </c>
       <c r="F12" t="n">
-        <v>42.17194</v>
+        <v>42.7982</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05131</v>
+        <v>0.05154</v>
       </c>
       <c r="H12" t="n">
-        <v>1.84107</v>
+        <v>1.80603</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.61768</v>
+        <v>16.70618</v>
       </c>
       <c r="D13" t="n">
-        <v>16.64314</v>
+        <v>16.60905</v>
       </c>
       <c r="E13" t="n">
-        <v>16.3213</v>
+        <v>16.6229</v>
       </c>
       <c r="F13" t="n">
-        <v>42.59644</v>
+        <v>42.49769</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05083</v>
+        <v>0.0509</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8272</v>
+        <v>1.82437</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.63459</v>
+        <v>16.83568</v>
       </c>
       <c r="D14" t="n">
-        <v>16.59162</v>
+        <v>16.65386</v>
       </c>
       <c r="E14" t="n">
-        <v>16.74944</v>
+        <v>16.66634</v>
       </c>
       <c r="F14" t="n">
-        <v>41.45811</v>
+        <v>42.54352</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05103</v>
+        <v>0.05164</v>
       </c>
       <c r="H14" t="n">
-        <v>1.80764</v>
+        <v>1.81925</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.7752</v>
+        <v>17.12626</v>
       </c>
       <c r="D15" t="n">
-        <v>16.74517</v>
+        <v>16.41266</v>
       </c>
       <c r="E15" t="n">
-        <v>16.53719</v>
+        <v>16.92621</v>
       </c>
       <c r="F15" t="n">
-        <v>43.06536</v>
+        <v>42.27136</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05073</v>
+        <v>0.05016</v>
       </c>
       <c r="H15" t="n">
-        <v>1.84838</v>
+        <v>1.81443</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.14597</v>
+        <v>16.61932</v>
       </c>
       <c r="D16" t="n">
-        <v>17.08877</v>
+        <v>16.45546</v>
       </c>
       <c r="E16" t="n">
-        <v>16.34176</v>
+        <v>16.60016</v>
       </c>
       <c r="F16" t="n">
-        <v>43.33466</v>
+        <v>43.15884</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05141</v>
+        <v>0.05092</v>
       </c>
       <c r="H16" t="n">
-        <v>1.81815</v>
+        <v>1.83607</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.81387</v>
+        <v>17.10189</v>
       </c>
       <c r="D17" t="n">
-        <v>16.5838</v>
+        <v>16.49854</v>
       </c>
       <c r="E17" t="n">
-        <v>16.74635</v>
+        <v>16.57591</v>
       </c>
       <c r="F17" t="n">
-        <v>43.15249</v>
+        <v>42.4257</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05042</v>
+        <v>0.05044</v>
       </c>
       <c r="H17" t="n">
-        <v>1.78306</v>
+        <v>1.82397</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.14896</v>
+        <v>16.83238</v>
       </c>
       <c r="D18" t="n">
-        <v>16.75187</v>
+        <v>16.60461</v>
       </c>
       <c r="E18" t="n">
-        <v>16.37648</v>
+        <v>16.74772</v>
       </c>
       <c r="F18" t="n">
-        <v>42.57938</v>
+        <v>42.49994</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05</v>
+        <v>0.04933</v>
       </c>
       <c r="H18" t="n">
-        <v>1.83441</v>
+        <v>1.86306</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.84893</v>
+        <v>16.76891</v>
       </c>
       <c r="D19" t="n">
-        <v>16.88749</v>
+        <v>16.48747</v>
       </c>
       <c r="E19" t="n">
-        <v>16.41254</v>
+        <v>16.49077</v>
       </c>
       <c r="F19" t="n">
-        <v>42.60977</v>
+        <v>42.30386</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05035</v>
+        <v>0.05091</v>
       </c>
       <c r="H19" t="n">
-        <v>1.80937</v>
+        <v>1.82568</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>17.05646</v>
-      </c>
-      <c r="D20" t="n">
-        <v>16.65682</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.34311</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.66819</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05028</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.83348</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Rz mean</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Rz min</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Rz max</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Ra max</t>
-        </is>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>0.60503</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.10025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>roughness</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.72628</v>
+        <v>0.6069600000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.08065</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.59698</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.98504</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.10937</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09447</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12658</v>
+        <v>1.0969</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.74575</v>
+        <v>0.61704</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08287</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.6133999999999999</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.95477</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.10921</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.00749</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.09285</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.12967</v>
+        <v>1.09891</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.74634</v>
+        <v>0.60761</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08103</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.60328</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.96612</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.10544</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.00768</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.09458999999999999</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.12693</v>
+        <v>1.11787</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.73655</v>
+        <v>0.6037</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0808</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.6023500000000001</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.9528</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.11149</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.00765</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.09356</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0.12822</v>
+        <v>1.10701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.7478399999999999</v>
+        <v>0.61341</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08064</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.60993</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.97299</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.11004</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.00764</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.09112000000000001</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.12703</v>
+        <v>1.12523</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.75127</v>
+        <v>0.5952</v>
       </c>
       <c r="D27" t="n">
-        <v>0.07853</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.61881</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.97177</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.10941</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.09322999999999999</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.12709</v>
+        <v>1.10913</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 2</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.73039</v>
+        <v>0.60647</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08287</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.60051</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.97085</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.11061</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.00759</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0.12653</v>
+        <v>1.12531</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6056</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1.12716</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.76829</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08117000000000001</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.60324</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.94055</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.10755</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09304999999999999</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.1248</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.74268</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.08143</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6097900000000001</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.96162</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.10894</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.09177</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.12614</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>0.74274</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.08193</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.61716</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.97135</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.10859</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.00762</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.09296</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.12503</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.7548</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.08154</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6166</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.95927</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.11121</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.00741</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.09236999999999999</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.12458</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.75158</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.08180999999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.62316</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.96622</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.10906</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.00771</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.09301</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.12864</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.75232</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.08031000000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.59428</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.94469</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.10961</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.00761</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.09402000000000001</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.12809</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.77806</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.08097</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.60845</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.93375</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.00758</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.09304999999999999</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.12721</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Unit 2</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0.75042</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.07979</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.61383</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.96867</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.10739</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.0077</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.0912</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.12356</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="C38" t="n">
+        <v>0.75034</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6103499999999999</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.94235</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.11076</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.09254</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.12702</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.73582</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.07889</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.6107</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.96912</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10693</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00743</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.09272</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12697</v>
+      <c r="C39" t="n">
+        <v>0.74173</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.07937</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.60876</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.96732</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.10566</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.09050999999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.12676</v>
       </c>
     </row>
   </sheetData>
